--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_biobio.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_biobio.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:45</t>
+    <t xml:space="preserve">2026-10-05 02:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>264452.38</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>279147.84</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>284359.59</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>318849.12</v>
+        <v>318849.13</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>363139.97</v>
@@ -1196,7 +1196,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>320006.12</v>
+        <v>320006.13</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>362756.59</v>
@@ -1229,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>340998.12</v>
+        <v>340998.13</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>378751.16</v>
@@ -1287,7 +1287,7 @@
         <v>356172.06</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1493,7 +1493,7 @@
         <v>75</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>392446.12</v>
+        <v>392446.13</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442966.53</v>
@@ -1529,7 +1529,7 @@
         <v>390538.72</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>398690.38</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
